--- a/artfynd/A 70205-2021 artfynd.xlsx
+++ b/artfynd/A 70205-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 70205-2021 artfynd.xlsx
+++ b/artfynd/A 70205-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>96389472</v>
       </c>
       <c r="B2" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442664.4767829976</v>
+        <v>442664</v>
       </c>
       <c r="R2" t="n">
-        <v>7054040.109011921</v>
+        <v>7054040</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2021-09-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>96389487</v>
       </c>
       <c r="B3" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442634.5103746619</v>
+        <v>442635</v>
       </c>
       <c r="R3" t="n">
-        <v>7054107.845554289</v>
+        <v>7054108</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,19 +847,9 @@
           <t>2021-09-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96389493</v>
+        <v>96389448</v>
       </c>
       <c r="B4" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442631.7596036588</v>
+        <v>442718</v>
       </c>
       <c r="R4" t="n">
-        <v>7054152.839291448</v>
+        <v>7053903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,19 +948,9 @@
           <t>2021-09-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96389467</v>
+        <v>96389493</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442677.4350143095</v>
+        <v>442632</v>
       </c>
       <c r="R5" t="n">
-        <v>7054042.099785085</v>
+        <v>7054153</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1049,9 @@
           <t>2021-09-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96389495</v>
+        <v>96389477</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442631.7596036588</v>
+        <v>442724</v>
       </c>
       <c r="R6" t="n">
-        <v>7054152.839291448</v>
+        <v>7054028</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,19 +1150,9 @@
           <t>2021-09-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96389454</v>
+        <v>96389495</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442681.7096108634</v>
+        <v>442632</v>
       </c>
       <c r="R7" t="n">
-        <v>7053933.440196649</v>
+        <v>7054153</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,19 +1251,9 @@
           <t>2021-09-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,470 +1278,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>96389477</v>
-      </c>
-      <c r="B8" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Nästsjön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>442723.5206921738</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7054027.917069906</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>96389464</v>
-      </c>
-      <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Nästsjön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>442615.1448030676</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7053973.360142295</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>96389448</v>
-      </c>
-      <c r="B10" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Nästsjön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>442718.1448231597</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7053902.965660946</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>96389461</v>
-      </c>
-      <c r="B11" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Nästsjön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>442656.8861532471</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7053989.96058444</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 70205-2021 artfynd.xlsx
+++ b/artfynd/A 70205-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96389472</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96389487</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96389493</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96389495</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96389448</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,8 +1308,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96389477</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>